--- a/Students/students_template.xlsx
+++ b/Students/students_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
           <t>medicalPin</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>className</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -524,8 +529,6 @@
           <t>+27831234567</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Peanuts</t>
@@ -549,6 +552,11 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>1234</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
         </is>
       </c>
     </row>
@@ -578,10 +586,6 @@
           <t>+27729876543</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>None</t>
@@ -605,6 +609,11 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>2222</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
@@ -644,8 +653,6 @@
           <t>+27834445555</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Asthma (inhaler required)</t>
@@ -669,6 +676,11 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>3333</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
         </is>
       </c>
     </row>
@@ -698,10 +710,6 @@
           <t>+27720112233</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>None</t>
@@ -725,6 +733,11 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>4444</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
         </is>
       </c>
     </row>
@@ -754,10 +767,6 @@
           <t>+27727894561</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Milk allergy</t>
@@ -781,6 +790,11 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>5555</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
@@ -810,10 +824,6 @@
           <t>+27728765432</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>None</t>
@@ -837,6 +847,11 @@
       <c r="N7" t="inlineStr">
         <is>
           <t>6666</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
         </is>
       </c>
     </row>
@@ -866,10 +881,6 @@
           <t>+27724561234</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Egg allergy</t>
@@ -893,6 +904,11 @@
       <c r="N8" t="inlineStr">
         <is>
           <t>7777</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
         </is>
       </c>
     </row>
@@ -922,10 +938,6 @@
           <t>+27723334444</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>None</t>
@@ -949,6 +961,11 @@
       <c r="N9" t="inlineStr">
         <is>
           <t>8888</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
@@ -978,10 +995,6 @@
           <t>+27726667777</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Seafood allergy</t>
@@ -1005,6 +1018,11 @@
       <c r="N10" t="inlineStr">
         <is>
           <t>9999</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
         </is>
       </c>
     </row>
@@ -1034,10 +1052,6 @@
           <t>+27725556666</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>None</t>
@@ -1061,6 +1075,11 @@
       <c r="N11" t="inlineStr">
         <is>
           <t>2468</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
         </is>
       </c>
     </row>
@@ -1090,10 +1109,6 @@
           <t>+27724443332</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Penicillin allergy</t>
@@ -1117,6 +1132,11 @@
       <c r="N12" t="inlineStr">
         <is>
           <t>1357</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
@@ -1146,10 +1166,6 @@
           <t>+27723332221</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>None</t>
@@ -1173,6 +1189,11 @@
       <c r="N13" t="inlineStr">
         <is>
           <t>1212</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
         </is>
       </c>
     </row>
@@ -1202,10 +1223,6 @@
           <t>+27728889999</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Peanuts</t>
@@ -1229,6 +1246,11 @@
       <c r="N14" t="inlineStr">
         <is>
           <t>2323</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1280,6 @@
           <t>+27727776665</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>None</t>
@@ -1285,6 +1303,11 @@
       <c r="N15" t="inlineStr">
         <is>
           <t>3434</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
@@ -1314,10 +1337,6 @@
           <t>+27726665554</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Lactose intolerance</t>
@@ -1341,6 +1360,11 @@
       <c r="N16" t="inlineStr">
         <is>
           <t>4545</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
         </is>
       </c>
     </row>
@@ -1370,10 +1394,6 @@
           <t>+27725554443</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>None</t>
@@ -1397,6 +1417,11 @@
       <c r="N17" t="inlineStr">
         <is>
           <t>5656</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
         </is>
       </c>
     </row>
@@ -1426,10 +1451,6 @@
           <t>+27724443322</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Bee sting allergy</t>
@@ -1453,6 +1474,11 @@
       <c r="N18" t="inlineStr">
         <is>
           <t>6767</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
@@ -1482,10 +1508,6 @@
           <t>+27723332211</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>None</t>
@@ -1509,6 +1531,11 @@
       <c r="N19" t="inlineStr">
         <is>
           <t>7878</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Little Explorers</t>
         </is>
       </c>
     </row>
@@ -1538,10 +1565,6 @@
           <t>+27722221110</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Tree nut allergy</t>
@@ -1565,6 +1588,11 @@
       <c r="N20" t="inlineStr">
         <is>
           <t>8989</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sunshine Bunnies</t>
         </is>
       </c>
     </row>
@@ -1594,10 +1622,6 @@
           <t>+27721110009</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>None</t>
@@ -1621,6 +1645,11 @@
       <c r="N21" t="inlineStr">
         <is>
           <t>9090</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Rainbow Cubs</t>
         </is>
       </c>
     </row>
